--- a/artfynd/A 54313-2023 artfynd.xlsx
+++ b/artfynd/A 54313-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121112708</v>
       </c>
       <c r="B2" t="n">
-        <v>74644</v>
+        <v>74647</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>121112698</v>
       </c>
       <c r="B3" t="n">
-        <v>90705</v>
+        <v>90715</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 54313-2023 artfynd.xlsx
+++ b/artfynd/A 54313-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121112708</v>
+        <v>121112698</v>
       </c>
       <c r="B2" t="n">
-        <v>74647</v>
+        <v>90727</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459743</v>
+        <v>459719</v>
       </c>
       <c r="R2" t="n">
-        <v>6988076</v>
+        <v>6988098</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121112698</v>
+        <v>121112708</v>
       </c>
       <c r="B3" t="n">
-        <v>90715</v>
+        <v>74649</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459719</v>
+        <v>459743</v>
       </c>
       <c r="R3" t="n">
-        <v>6988098</v>
+        <v>6988076</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 54313-2023 artfynd.xlsx
+++ b/artfynd/A 54313-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121112698</v>
       </c>
       <c r="B2" t="n">
-        <v>90727</v>
+        <v>90728</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 54313-2023 artfynd.xlsx
+++ b/artfynd/A 54313-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121112698</v>
+        <v>121112708</v>
       </c>
       <c r="B2" t="n">
-        <v>90728</v>
+        <v>74652</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459719</v>
+        <v>459743</v>
       </c>
       <c r="R2" t="n">
-        <v>6988098</v>
+        <v>6988076</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121112708</v>
+        <v>121112698</v>
       </c>
       <c r="B3" t="n">
-        <v>74649</v>
+        <v>90731</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459743</v>
+        <v>459719</v>
       </c>
       <c r="R3" t="n">
-        <v>6988076</v>
+        <v>6988098</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 54313-2023 artfynd.xlsx
+++ b/artfynd/A 54313-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121112708</v>
+        <v>121112698</v>
       </c>
       <c r="B2" t="n">
-        <v>74652</v>
+        <v>90731</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459743</v>
+        <v>459719</v>
       </c>
       <c r="R2" t="n">
-        <v>6988076</v>
+        <v>6988098</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121112698</v>
+        <v>121112708</v>
       </c>
       <c r="B3" t="n">
-        <v>90731</v>
+        <v>74652</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459719</v>
+        <v>459743</v>
       </c>
       <c r="R3" t="n">
-        <v>6988098</v>
+        <v>6988076</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
